--- a/Template Alih Status Kolektif.xlsx
+++ b/Template Alih Status Kolektif.xlsx
@@ -168,7 +168,7 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomor DPB</t>
+          <t xml:space="preserve">Nomor DPS</t>
         </is>
       </c>
     </row>
@@ -265,7 +265,7 @@
       </c>
       <c r="S2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DPB-004133</t>
+          <t xml:space="preserve">000133</t>
         </is>
       </c>
     </row>
@@ -362,7 +362,7 @@
       </c>
       <c r="S3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DPB-004129</t>
+          <t xml:space="preserve">000129</t>
         </is>
       </c>
     </row>
